--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/1_Finance_and_Capital_Mobilization.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/1_Finance_and_Capital_Mobilization.xlsx
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2563000</v>
+        <v>2253000</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>284777.7777777778</v>
+        <v>281625</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>285000</v>
+        <v>200000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>205000</v>
+        <v>175000</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1184000</v>
+        <v>1139000</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>319000</v>
+        <v>309000</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>360000</v>
+        <v>320000</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>80000</v>
@@ -817,14 +817,14 @@
       <c r="R4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="7" t="n">
-        <v>100000</v>
+      <c r="S4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="T4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2703000</v>
+        <v>2293000</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>450500</v>
+        <v>458600</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>520000</v>
+        <v>440000</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>261000</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1060000</v>
+        <v>860000</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>0</v>
@@ -868,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>382000</v>
+        <v>292000</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>180000</v>
+        <v>140000</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>70000</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>483000</v>
+        <v>73000</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>241500</v>
+        <v>73000</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>92000</v>
+        <v>12000</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>231000</v>
+        <v>31000</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0</v>
@@ -932,11 +932,11 @@
       <c r="M6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>90000</v>
+      <c r="N6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1447,16 +1447,16 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3880501</v>
+        <v>3862501</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>228264.7647058823</v>
+        <v>275892.9285714286</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1541501</v>
+        <v>1523501</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>258000</v>
@@ -1641,23 +1641,23 @@
           <t>E-mitra</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>470000</v>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>470000</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>68000</v>
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>256000</v>
+      <c r="I17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0</v>
@@ -1671,14 +1671,14 @@
       <c r="M17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O17" s="7" t="n">
-        <v>48000</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>48000</v>
+      <c r="N17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>0</v>
@@ -1692,8 +1692,8 @@
       <c r="T17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="6" t="n">
-        <v>1</v>
+      <c r="U17" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2449500</v>
+        <v>2198500</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>378000</v>
+        <v>348000</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>1771000</v>
+        <v>1571000</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>0</v>
@@ -3058,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>859000</v>
+        <v>759000</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>360000</v>
+        <v>280000</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>30000</v>
@@ -3072,8 +3072,8 @@
       <c r="O41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P41" s="7" t="n">
-        <v>100000</v>
+      <c r="P41" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" s="7" t="n">
         <v>70000</v>
@@ -3099,7 +3099,7 @@
         <v>1000</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>654000</v>
+        <v>398000</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>0</v>
@@ -3114,13 +3114,13 @@
         <v>0</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>262000</v>
+        <v>212000</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>358000</v>
+        <v>310000</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>78000</v>
+        <v>30000</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>50000</v>
@@ -3155,7 +3155,7 @@
         <v>61000</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>419000</v>
+        <v>374000</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>0</v>

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/1_Finance_and_Capital_Mobilization.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/excel_exports/1_Finance_and_Capital_Mobilization.xlsx
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2253000</v>
+        <v>1621000</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>281625</v>
+        <v>231571.4285714286</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1139000</v>
+        <v>729000</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0</v>
@@ -797,16 +797,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>309000</v>
+        <v>252000</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>80000</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -902,23 +902,23 @@
           <t>Apparel/fabric</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>73000</v>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>73000</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>12000</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>31000</v>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0</v>
@@ -935,8 +935,8 @@
       <c r="N6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="7" t="n">
-        <v>30000</v>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>0</v>
@@ -953,8 +953,8 @@
       <c r="T6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="6" t="n">
-        <v>1</v>
+      <c r="U6" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
